--- a/public/results/result.xlsx
+++ b/public/results/result.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,39 +424,39 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ALAM</v>
+        <v>NAIMULALAM</v>
       </c>
       <c r="B2" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>10/8/2025, 4:03:03 PM</v>
+        <v>9/26/2026, 4:56:46 PM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>NAIM</v>
+        <v>Guest</v>
       </c>
       <c r="B3" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -465,21 +465,21 @@
         <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>10/8/2025, 4:05:32 PM</v>
+        <v>9/26/2026, 5:14:18 PM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SAKIB</v>
+        <v>Guest</v>
       </c>
       <c r="B4" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -488,21 +488,21 @@
         <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>10/8/2025, 4:08:15 PM</v>
+        <v>9/26/2026, 5:23:20 PM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ALVIYA</v>
+        <v>MD NAIMUL ALAM</v>
       </c>
       <c r="B5" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>7</v>
@@ -511,44 +511,44 @@
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>10/8/2025, 4:10:44 PM</v>
+        <v>9/26/2026, 5:32:27 PM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sdfsdfsdf</v>
+        <v>MD NAIMUL ALAM</v>
       </c>
       <c r="B6" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>10/8/2025, 4:15:14 PM</v>
+        <v>9/26/2026, 5:36:09 PM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Guest</v>
+        <v>MD NAIMUL ALAM</v>
       </c>
       <c r="B7" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>7</v>
@@ -557,12 +557,12 @@
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>10/8/2025, 4:39:53 PM</v>
+        <v>9/26/2026, 5:56:27 PM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Guest</v>
+        <v>NAIM</v>
       </c>
       <c r="B8" t="str">
         <v>guest@example.com</v>
@@ -574,18 +574,18 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>10/8/2025, 4:46:17 PM</v>
+        <v>9/26/2026, 6:15:17 PM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Guest</v>
+        <v>NAIMUL ALAM</v>
       </c>
       <c r="B9" t="str">
         <v>guest@example.com</v>
@@ -597,18 +597,18 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>10/8/2025, 4:47:21 PM</v>
+        <v>9/26/2026, 6:17:29 PM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>asdasd</v>
+        <v>MD NAIMUL ALAM</v>
       </c>
       <c r="B10" t="str">
         <v>guest@example.com</v>
@@ -626,21 +626,21 @@
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>10/8/2025, 4:55:55 PM</v>
+        <v>9/26/2026, 6:45:33 PM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Guest</v>
+        <v>MD NAIMUL ALAM</v>
       </c>
       <c r="B11" t="str">
         <v>guest@example.com</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -649,58 +649,12 @@
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>10/8/2025, 4:58:57 PM</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Guest</v>
-      </c>
-      <c r="B12" t="str">
-        <v>guest@example.com</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>7</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="str">
-        <v>10/8/2025, 5:00:10 PM</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Guest</v>
-      </c>
-      <c r="B13" t="str">
-        <v>guest@example.com</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>7</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="str">
-        <v>10/8/2025, 5:02:21 PM</v>
+        <v>9/28/2026, 6:49:11 AM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
   </ignoredErrors>
 </worksheet>
 </file>